--- a/data/coding/coder1/P19.xlsx
+++ b/data/coding/coder1/P19.xlsx
@@ -19074,11 +19074,11 @@
       </c>
       <c r="E660" s="5" t="inlineStr">
         <is>
-          <t>효정님은 AI 대학원과 학연생을 목표로 하고 있으니까, 8월 동안 작은 포트폴리오를 하나 만드는 것을 추천합니다.</t>
+          <t>[이름]님은 AI 대학원과 학연생을 목표로 하고 있으니까, 8월 동안 작은 포트폴리오를 하나 만드는 것을 추천합니다.</t>
         </is>
       </c>
       <c r="F660" s="4" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G660" s="6" t="inlineStr"/>
       <c r="H660" s="6" t="inlineStr"/>
